--- a/data.xlsx
+++ b/data.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bưu cục A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bưu cục B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đơn vị A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đơn vị B" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,13 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,7 +445,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Vùng</t>
+          <t>Mã hàng</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -452,91 +455,187 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Số thứ tự</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tầng</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tên nhóm POG</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>893100000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vùng 1</t>
+          <t>8936228560892</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SP001234</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kệ A-01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Hàng nhẹ</t>
+          <t>Kệ lạnh L03</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>V2.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sữa chua</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>893100000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vùng 2</t>
+          <t>8936228560892</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SP001234</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kệ B-05</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Đầu kệ E01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V2.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Khuyến mãi tháng</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>893100000003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Vùng 2</t>
+          <t>8934673100016</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SP000871</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kệ B-06</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Hàng dễ vỡ</t>
+          <t>Kệ khô K12</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>V3.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Mì ăn liền</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>8932*</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Vùng 3</t>
+          <t>0123456789012</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SP000002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kệ C (theo đầu mã)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mọi mã bắt đầu bằng 8932</t>
+          <t>Kệ khô K01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>V3.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gia vị</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>8935*</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SP009999</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kệ tạp hoá T05</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>V1.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hàng tạp hoá (theo đầu mã 8935)</t>
         </is>
       </c>
     </row>
@@ -551,13 +650,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,7 +670,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Vùng</t>
+          <t>Mã hàng</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -578,49 +680,90 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Số thứ tự</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tầng</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tên nhóm POG</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>893100000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vùng 5</t>
+          <t>8936228560892</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SP001234</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ô 12</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Cùng mã nhưng khác đơn vị</t>
+          <t>Kệ mát M07</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>V1.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sữa chua</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>893100000009</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vùng 6</t>
+          <t>8934673100016</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SP000871</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ô 03</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Kệ khô K02</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V2.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mì ăn liền</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đơn vị A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đơn vị B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DanhSach" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,8 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -425,218 +428,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barcode</t>
+          <t>GĐ</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mã hàng</t>
+          <t>CONTENTS</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vị trí</t>
+          <t>FujiMart Le
+Duan</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Số thứ tự</t>
+          <t>FujiMart Tay Son</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tầng</t>
+          <t>FujiMart Hoang Cau</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tên nhóm POG</t>
+          <t>FujiMart Long Quan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>8936228560892</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>SP001234</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Kệ lạnh L03</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rượu (Wine)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sữa chua uống (Drink yogurt)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>V2.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sữa chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>8936228560892</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SP001234</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Đầu kệ E01</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>V2.1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Khuyến mãi tháng</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>8934673100016</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SP000871</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Kệ khô K12</t>
-        </is>
-      </c>
       <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cà phê (Coffee)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>V3.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Mì ăn liền</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>0123456789012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SP000002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Kệ khô K01</t>
-        </is>
-      </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>V3.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Gia vị</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>8935*</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SP009999</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Kệ tạp hoá T05</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>G2 - Conf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Snack, khoai tây chiên (Snack, French fries)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>V1.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hàng tạp hoá (theo đầu mã 8935)</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -650,119 +602,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Layer POG</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Item code</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Barcode</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Mã hàng</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Vị trí</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Số thứ tự</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Tầng</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tên nhóm POG</t>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Item Name</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>FujiMart Le Duan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>FujiMart Tay Son</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FujiMart Hoang Cau</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>FujiMart Long Quan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2001327074</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>8934673574341</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT hương dâu 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2001324865</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>8934673101363</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT dừa 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2001327143</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>8935217400362</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TH_Lốc sữa tươi TT ít đường 110mlx4 T12</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sữa chua uống (Drink yogurt)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2001500001</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>8936228560892</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>SP001234</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Kệ mát M07</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>V1.4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sữa chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>8934673100016</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SP000871</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Kệ khô K02</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>V2.8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Mì ăn liền</t>
-        </is>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Milana Creamy Yogurt 100ml</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>G1 - Drink</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cà phê (Coffee)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2001600002</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0123456789012</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cà phê hòa tan mẫu 20 gói</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>G2 - Conf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Snack, khoai tây chiên (Snack, French fries)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2002700003</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>94147803</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Snack mẫu 50g</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G2 - Conf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nhóm chưa có version (thử cảnh báo)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2002800004</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>8930000000019</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hàng thử nhóm thiếu version</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DanhSach" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ViTri" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,10 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -479,17 +480,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rượu (Wine)</t>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -503,92 +504,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
+          <t>Cà phê (Coffee)</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
       <c r="F3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>G1 - Drink</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sữa chua uống (Drink yogurt)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>G1 - Drink</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cà phê (Coffee)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="n">
         <v>1.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>G2 - Conf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Snack, khoai tây chiên (Snack, French fries)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -602,11 +531,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
@@ -672,17 +601,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2001327074</t>
+          <t>2001323674</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>8934673574341</t>
+          <t>8934673503327</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VNM_Lốc sữa tươi TT hương dâu 180mlx4 T12</t>
+          <t>Sữa tươi TT không đường Vinamilk hộp 110ml</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -711,17 +640,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2001324865</t>
+          <t>2001327128</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>8934673101363</t>
+          <t>8934673581325</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VNM_Lốc sữa tươi TT dừa 180mlx4 T12</t>
+          <t>VNM_Sữa tươi TT ít đường 110ml T48</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -750,17 +679,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2001327143</t>
+          <t>2001327068</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>8935217400362</t>
+          <t>8934673576345</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TH_Lốc sữa tươi TT ít đường 110mlx4 T12</t>
+          <t>VNM_Sữa TT không đường 180ml T48</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -784,29 +713,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sữa chua uống (Drink yogurt)</t>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2001500001</t>
+          <t>2001327115</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>8936228560892</t>
+          <t>8934673581349</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Milana Creamy Yogurt 100ml</t>
+          <t>VNM_Sữa TT ít đường 180ml T48</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -823,61 +752,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cà phê (Coffee)</t>
+          <t>Sữa tươi tiệt trùng (UHT Milk)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2001600002</t>
+          <t>2001096621</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0123456789012</t>
+          <t>8934673576390</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cà phê hòa tan mẫu 20 gói</t>
+          <t>C - Sữa tiệt trùng ko đường hộp 1L- đàn bò</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G2 - Conf</t>
+          <t>G1 - Drink</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Snack, khoai tây chiên (Snack, French fries)</t>
+          <t>Cà phê (Coffee)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2002700003</t>
+          <t>2001600002</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>94147803</t>
+          <t>0123456789012</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Snack mẫu 50g</t>
+          <t>Cà phê hòa tan mẫu 20 gói</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -890,46 +819,4681 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Item code</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Vị trí</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Tầng</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Số thứ tự</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Số mặt</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Tên hàng</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Sơ đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>8934673503327</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2001323674</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT không đường Vinamilk hộp 110ml</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>8934673581325</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2001327128</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT ít đường 110ml T48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>8934673576345</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2001327068</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT không đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>8934673581349</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2001327115</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT ít đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>8934673576345</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2001327068</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT không đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>8934673581349</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2001327115</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT ít đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G2 - Conf</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nhóm chưa có version (thử cảnh báo)</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>8934673576390</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2002800004</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>8930000000019</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hàng thử nhóm thiếu version</t>
-        </is>
+          <t>2001096621</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C - Sữa tiệt trùng ko đường hộp 1L- đàn bò</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>8934673581394</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2001247708</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>C - STTT ít đường VNM 1L*12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>8934673101097</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2001314311</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sữa TTT Không đường 100% sữa tươi F220ml</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>8934673574327</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2001327073</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT hương dâu 110ml T48</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>8934673575324</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2001327071</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT socola 110ml T48</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>8934673573344</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2001327067</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>8934673101363</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2001324865</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vinamilk-Sữa tươi tiệt trùng dừa 180ml</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>8934673574341</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2001327074</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT hương dâu 180ml T48</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>8934673573344</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2001327067</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>8934673101363</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2001324865</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vinamilk-Sữa tươi tiệt trùng dừa 180ml</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>8934673574341</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2001327074</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT hương dâu 180ml T48</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>8934673573399</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2001052570</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>C - Sữa tiệt trùng đường 1L đàn bò 100%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>8934673101080</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2001314310</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sữa TTT ít đường 100% sữa tươi F220ml</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>8934673101073</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2001314309</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sữa TTT có đường 100% sữa tươi F220ml</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>8934673100441</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2001327119</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VNM_ Sữa tươi TT ít đường Green Farm ST 100% 110ml T48</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>8934673100410</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2001327117</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT có đường Green Farm ST 100% 110mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>8934673575348</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2001327072</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT socola 180ml T48</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>8934673100588</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2001327089</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT không đường Green farm 180ml T48</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>8934673100458</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2001327120</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT ít đường Green Farm ST 100% 180ml T48</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>8934673100427</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2001327118</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT có đường Green Farm ST 100% 180ml T48</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>8934673101899</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2001330992</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT tách béo socola 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>8934673100939</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2001327121</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VNM_Sữa tươi TT ít béo không đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>8934673101356</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2001327086</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VNM_ Lốc sữa tươi TT giảm béo vị chuối 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>8934673101615</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2001330991</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT tách béo dưa lưới 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>8934673101264</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2001324847</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vinamilk-Sữa TT Green Farm Organic 1L</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>8934673100595</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2001318590</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT không đường Vinamilk Green Farm 1L</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>8934673502351</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2001194791</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>C - Sữa TT hương dâu VNM 220ml</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>8934673101424</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2001332824</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VNM_Sữa TT cao đạm ít béo Green farm 250ml T12</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>8934673101837</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2001331193</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT hương Pina Colada 240mlx3 T4</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>8934673101844</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2001331194</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT hương Bourbon Chuối Bơ đậu phộng 240mlx3 T4</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>8934673101851</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2001331195</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT hương Cà phê Ailen 240mlx3 T4</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>8934673101257</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2001324846</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vinamilk-Sữa TT Green Farm Organic 180ml</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>8934673101592</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>2001330989</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT Green Farm A2 không đường 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>8934673101400</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2001327087</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT tổ yến VNM Green farm 180mlx4</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>8934673101608</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2001330990</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa tươi TT Bắp 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>8934673101554</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2001330987</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VNM_Lốc sữa dinh dưỡng giàu canxi không Lactoza Flex 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>8936012063240</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2001331191</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mộc châu_Lốc Sữa tươi TT ít đường Creamery 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>8936012063189</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2001331192</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Mộc châu_Lốc Sữa tươi TT không đường Creamery 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>8934673100465</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2001318589</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT rất ít đường Vinamilk Green Farm 1L</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>8934673101561</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2001330988</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>VNM_Sữa dinh dưỡng giàu canxi không Lactoza Flex 1L T12</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>8934673503358</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2001194792</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C - Sữa TT SCL VNM F220ml</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>8935217400362</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2001327143</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT ít đường 110ml T48</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>8935217400164</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2001327161</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT có đường 110ml T48</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>8935217400058</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2001327139</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT ko đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>8935217400355</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2001327141</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TH_ Sữa tươi TT ít đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>8934841901849</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2001327018</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CGHL_Lốc sữa tươi TT ko đường 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>8934841901856</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2001327019</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CGHL_Lốc sữa tươi TT có đường 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>8934841901863</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>2001327020</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CGHL_Lốc sữa tươi TT vị dâu 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>8934841901870</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>2001327021</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CGHL_Lốc sữa tươi TT vị socola 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>8935217400027</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>2001187941</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng TH ko đường 1L</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>8935217400324</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2001187943</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng TH ít đường 1L</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>8935217400126</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2001187942</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng TH có đường 1L</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>8934841901962</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2001217478</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CGHL_Sữa tươi TT có đường hộp 965ml T12</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>8934841901979</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>2001217477</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CGHL_Sữa tươi TT không đường hộp 965ml T12</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>4810319016465</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2001316159</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sữa Minskaya tươi tiệt trùng nguyên kem 3.2% 1L</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>8935217400393</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2001228812</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng ít đường TH 220ml</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>8935217400195</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2001228813</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng có đường TH 220ml</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>8935217400096</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2001228811</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng nguyên chất TH 220ml</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>8935217400065</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2001327159</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT nguyên chất 110ml T48</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>8935217400263</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>2001327162</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT hương dâu 110ml T48</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>8935217400461</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>2001327157</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>6</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT vị SCL 110ml T48</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>8938503131919</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>2001327148</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Dalatmilk_Sữa tươi TT ít đường 110ml T48</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>8935217400157</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>2001327140</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT có đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>8935217400256</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>2001327142</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT hương dâu 180ml T48</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>8935217400454</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>2001327158</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT vị SCL 180ml T48</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>8935217407156</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>2001327168</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>6</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TH_Sữa tươi TT vị tự nhiên Hilo 180ml T48</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>8936036773439</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>2001224010</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CGHL_ Lốc sữa tươi TT có đường cao khỏe 170mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>8934841902099</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>2001316447</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CGHL_Lốc sữa tươi TT cao khỏe hương dâu 170mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>8934841903799</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>2001332954</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CGHL_ Lốc sữa tươi TT ít đường cao khỏe 170mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>8936012063448</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>2001332347</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Mộc châu_Lốc Sữa tươi TT hương cam Creamery 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>8936203350012</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>2001302203</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>6</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>C - Lốc 4 hộp sữa tươi tiệt trùng UHT-Đà lạt True Milk ít đường</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>9315090212709</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>2001324267</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>6</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sữa tiệt trùng nguyên kem Milklab 1L</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>9415522285001</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>2001282442</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi TT nguyên kem Meadow 1Lx12</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>9415522001274</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>2001282444</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT ít béo Meadow 1Lx12</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>9415522285049</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>2001282447</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT giàu cannxi ít béo Meadow 1Lx12</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>94147803</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>2001237575</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sữa tươi nguyên kem hộp 1L</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>5701215046832</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>2001253732</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sữa tươi nguyên chất tiệt trùng nguyên kem -Emborg 1l</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>5900512901954</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>2001329820</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Mlekovita_Sữa tiệt trùng nguyên kem A2A2 3.8% hộp 1L T12</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>5900512990262</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>2001320306</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sữa Mlekovita Full Cream  3.5% 1L</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>5901062002702</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>2001328718</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>9</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Mlekovita_Sữa tươi TT tách béo 1.5% hộp 1L T12</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>8934841902822</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2001290590</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CGHL_Sữa tươi TT cao khỏe Fino bịch 180ml T24</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>8934841902914</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>2001316446</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CGHL_Sữa tươi TT ít đường bịch 180ml T24</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>8938503131933</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>2001284325</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng ít đường 220ml Dalatmilk</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>8938503131759</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>2001284326</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng có đường 220ml Dalatmilk</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>8938503131827</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>2001327149</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>7</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Dalatmilk_Sữa tươi TT có đường 110ml T48</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>4810319020028</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>2001331336</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Slavyanskiye_Lốc sữa tươi tiệt trùng Traditsiyi 3.2% chất béo 200ml x4 T6</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>9315090213881</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>2001326969</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>7</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Own_Sữa tươi nguyên chất TT A2 200mlx3 T8</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>9315090213874</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>2001332516</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Australia's Own_Lốc Sữa tươi TT nguyên kem 200mlx3 T8</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>9300639609911</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>2001227364</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Devondale _Lốc Sữa tươi TT nguyên chất 200mlx6 T4</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>8938503131995</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>2001327163</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>7</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Dalatmilk_Sữa tươi TT vị tự nhiên 180ml T48</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>8938503131926</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2001327164</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Dalatmilk_Sữa tươi TT ít đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>8938503131834</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>2001327165</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>7</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dalatmilk_Sữa tươi TT có đường 180ml T48</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>8938549701022</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2001327327</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Oldenburger_Sữa tươi tiệt trùng có đường 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>8936203350029</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>2001302204</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng UHT-Đà lạt True Milk không đường 180ml</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>8936203350548</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>2001321163</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>7</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sữa Tiệt trùng VP Milk Omega ít  đường hộp 180ml</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>8936203350562</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>2001321162</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sữa Tiệt trùng VP Milk Omega có đường hộp 180ml</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>8938549701053</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>2001327326</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Oldenburger_Sữa tươi tiệt trùng ít đường 180mlx4 T12</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>8410285127347</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>2001324796</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>7</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sữa President Full Cream  3.5% 1L</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>9353809000988</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>2001321698</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>7</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sữa Au King Care Full Cream 3.5% 1L</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>8888440007108</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>2001290592</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>7</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sữa tươi TT ít béo  Cowhead 1L</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>8888440000048</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>2001290591</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi TT nguyên chất Cowhead 1L</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>4036300669452</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>2001327324</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Oldenburger_Sữa tươi tiệt trùng nguyên kem (3.5% béo) hộp 1L T12</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>4036300069467</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>2001327325</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Oldenburger_Sữa tươi tiệt trùng ít béo (1.5% béo) hộp 1L T12</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>9315090206975</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>2001326970</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="n">
+        <v>7</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Own_Sữa tươi nguyên chất TT A2 1L T12</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>9315090206944</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>2001276880</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Australia's Own_Sữa tươi TT nguyên kem 1l T12</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>9300639618661</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2001332952</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Liddells _Sữa tươi TT nguyên kem không Lactose  hộp 1L T10</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>9300639618678</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2001332953</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Liddells _Sữa tươi TT ít béo không Lactose  hộp 1L T10</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>9300639603018</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>2001003327</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Devondale _Sữa tươi TT nguyên chất hộp 1L T10</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>8938503131957</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>2001284324</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>C - Sữa tươi tiệt trùng vị tự nhiên Dalatmilk 220ml</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>8936203350036</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>2001301197</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>C - Sữa tiệt trùng VP Milk Omega không đường 220ml</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>8936203350043</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>2001301198</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7</v>
+      </c>
+      <c r="E118" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>C - Sữa tiệt trùng VP Milk Omega ít đường 220ml</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>8936203350050</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>2001301199</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>7</v>
+      </c>
+      <c r="E119" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>C - Sữa tiệt trùng VP Milk Omega có đường 220ml</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>7. Sữa UHT</t>
+        </is>
       </c>
     </row>
   </sheetData>
